--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260810.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>14.24%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.54%</t>
+          <t>12.55%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>902,277,000</t>
+          <t>905,277,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.94%</t>
+          <t>10.96%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>9.87%</t>
+          <t>10.22%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,194,800,000</t>
+          <t>1,198,800,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.76%</t>
+          <t>7.83%</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>35,660,000</t>
+          <t>36,100,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>804,090,000</t>
+          <t>811,260,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.59%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.85%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.64%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -858,73 +858,73 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,036</t>
+          <t>11,430,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>11,430,000</t>
+          <t>73,440,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>73,440,000</t>
+          <t>720</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>119,300,000</t>
+          <t>82,480,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,154 +1041,154 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>119,300,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>81,480,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>12,468,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>76,770,000</t>
+          <t>12,468,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>8,504,000</t>
+          <t>76,770,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>8,504,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1217,39 +1217,39 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>36,740,000</t>
+          <t>27,842,899</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>29,940,000</t>
+          <t>36,740,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>27,842,899</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,105 +1305,105 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>29,940,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>15,470,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>15,470,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,61 +1437,61 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>20,540,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20,540,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>4,812,189,311</t>
+          <t>4,224,938,626</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,702,069,195</t>
+          <t>1,873,640,721</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>-224,413,485</t>
+          <t>-60,180,648</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>-944,671,225</t>
+          <t>-1,430,883,971</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
